--- a/untranslated/downloads/data-excel/3.7.2.xlsx
+++ b/untranslated/downloads/data-excel/3.7.2.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41608A27-2133-4607-9EE3-564D900B6F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23130" windowHeight="9450"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="15-19 лет рожд." sheetId="3" r:id="rId1"/>
@@ -185,7 +186,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
@@ -424,7 +425,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -437,58 +438,50 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -502,111 +495,101 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 2" xfId="1"/>
-    <cellStyle name="Обычный 4" xfId="7"/>
-    <cellStyle name="Обычный 5" xfId="6"/>
-    <cellStyle name="Обычный 6" xfId="8"/>
-    <cellStyle name="Обычный 7" xfId="2"/>
-    <cellStyle name="Обычный_Браки" xfId="5"/>
-    <cellStyle name="Обычный_КАБАН" xfId="4"/>
-    <cellStyle name="Обычный_Мат" xfId="3"/>
+    <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Обычный 4" xfId="7" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Обычный 5" xfId="6" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Обычный 6" xfId="8" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Обычный 7" xfId="2" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Обычный_Браки" xfId="5" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Обычный_КАБАН" xfId="4" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="Обычный_Мат" xfId="3" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -622,7 +605,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="ОШ-обл"/>
@@ -3923,7 +3906,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Лист1"/>
@@ -7242,7 +7225,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Нар-обл"/>
@@ -10543,9 +10526,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -10583,9 +10566,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -10620,7 +10603,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -10655,7 +10638,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -10828,7 +10811,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:V24"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
@@ -10839,98 +10822,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" customFormat="1" ht="57.75" customHeight="1">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="54" t="s">
+      <c r="B1" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="52" t="s">
+      <c r="C1" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51"/>
-      <c r="K1" s="51"/>
-      <c r="L1" s="51"/>
-      <c r="M1" s="51"/>
-      <c r="N1" s="51"/>
     </row>
     <row r="2" spans="1:22" ht="16.5" customHeight="1" thickBot="1"/>
     <row r="3" spans="1:22" s="3" customFormat="1" ht="18" customHeight="1" thickBot="1">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="28">
+      <c r="D3" s="25">
         <v>2007</v>
       </c>
-      <c r="E3" s="28">
+      <c r="E3" s="25">
         <v>2008</v>
       </c>
-      <c r="F3" s="28">
+      <c r="F3" s="25">
         <v>2009</v>
       </c>
-      <c r="G3" s="28">
+      <c r="G3" s="25">
         <v>2010</v>
       </c>
-      <c r="H3" s="28">
+      <c r="H3" s="25">
         <v>2011</v>
       </c>
-      <c r="I3" s="29">
+      <c r="I3" s="25">
         <v>2012</v>
       </c>
-      <c r="J3" s="29">
+      <c r="J3" s="25">
         <v>2013</v>
       </c>
-      <c r="K3" s="29">
+      <c r="K3" s="25">
         <v>2014</v>
       </c>
-      <c r="L3" s="28">
+      <c r="L3" s="25">
         <v>2015</v>
       </c>
-      <c r="M3" s="29">
+      <c r="M3" s="25">
         <v>2016</v>
       </c>
-      <c r="N3" s="29">
+      <c r="N3" s="25">
         <v>2017</v>
       </c>
-      <c r="O3" s="29">
+      <c r="O3" s="25">
         <v>2018</v>
       </c>
-      <c r="P3" s="29">
+      <c r="P3" s="25">
         <v>2019</v>
       </c>
-      <c r="Q3" s="29">
+      <c r="Q3" s="25">
         <v>2020</v>
       </c>
-      <c r="R3" s="29">
+      <c r="R3" s="25">
         <v>2021</v>
       </c>
-      <c r="S3" s="29">
+      <c r="S3" s="25">
         <v>2022</v>
       </c>
-      <c r="T3" s="29">
+      <c r="T3" s="25">
         <v>2023</v>
+      </c>
+      <c r="U3" s="25">
+        <v>2024</v>
       </c>
     </row>
     <row r="4" spans="1:22" s="3" customFormat="1" ht="15" customHeight="1">
-      <c r="A4" s="31" t="s">
+      <c r="A4" s="27" t="s">
         <v>13</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="30" t="s">
         <v>23</v>
       </c>
       <c r="D4" s="5">
@@ -10948,10 +10923,10 @@
       <c r="H4" s="8">
         <v>41.4</v>
       </c>
-      <c r="I4" s="9">
+      <c r="I4" s="8">
         <v>42.1</v>
       </c>
-      <c r="J4" s="10">
+      <c r="J4" s="9">
         <v>41.9</v>
       </c>
       <c r="K4" s="8">
@@ -10963,95 +10938,98 @@
       <c r="M4" s="8">
         <v>38.1</v>
       </c>
-      <c r="N4" s="25">
+      <c r="N4" s="22">
         <v>33.9</v>
       </c>
-      <c r="O4" s="25">
+      <c r="O4" s="22">
         <v>35.9</v>
       </c>
-      <c r="P4" s="56">
+      <c r="P4" s="46">
         <v>37.700000000000003</v>
       </c>
-      <c r="Q4" s="56">
+      <c r="Q4" s="46">
         <v>33.4</v>
       </c>
-      <c r="R4" s="58">
+      <c r="R4" s="48">
         <v>29.684644672533683</v>
       </c>
-      <c r="S4" s="58">
+      <c r="S4" s="48">
         <v>30.042887362716971</v>
       </c>
-      <c r="T4" s="58">
+      <c r="T4" s="48">
         <v>28.85</v>
       </c>
+      <c r="U4" s="48">
+        <v>26.38</v>
+      </c>
     </row>
-    <row r="5" spans="1:22" s="67" customFormat="1" ht="15">
-      <c r="A5" s="63" t="s">
+    <row r="5" spans="1:22" s="56" customFormat="1" ht="15">
+      <c r="A5" s="52" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="64" t="s">
+      <c r="B5" s="53" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="64" t="s">
+      <c r="C5" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="D5" s="65"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
     </row>
     <row r="6" spans="1:22" s="3" customFormat="1" ht="15" customHeight="1">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="11">
         <v>23.732590529247911</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="11">
         <v>24.367891934493535</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="12">
         <v>27.880113592754626</v>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="13">
         <v>32.913553895410885</v>
       </c>
-      <c r="H6" s="15">
+      <c r="H6" s="14">
         <v>39.05806586125815</v>
       </c>
-      <c r="I6" s="16">
+      <c r="I6" s="14">
         <v>43.933106378749102</v>
       </c>
-      <c r="J6" s="17">
+      <c r="J6" s="15">
         <v>45.236454418973565</v>
       </c>
-      <c r="K6" s="11">
+      <c r="K6" s="10">
         <v>45.1</v>
       </c>
-      <c r="L6" s="11">
+      <c r="L6" s="10">
         <v>39.700000000000003</v>
       </c>
-      <c r="M6" s="11">
+      <c r="M6" s="10">
         <v>37.6</v>
       </c>
-      <c r="N6" s="11">
+      <c r="N6" s="10">
         <v>35.6</v>
       </c>
-      <c r="O6" s="11">
+      <c r="O6" s="10">
         <v>38.799999999999997</v>
       </c>
-      <c r="P6" s="11">
+      <c r="P6" s="10">
         <v>43.1</v>
       </c>
-      <c r="Q6" s="11">
+      <c r="Q6" s="10">
         <v>37.299999999999997</v>
       </c>
-      <c r="R6" s="59">
+      <c r="R6" s="49">
         <v>36.9</v>
       </c>
       <c r="S6" s="3">
@@ -11060,60 +11038,63 @@
       <c r="T6" s="3">
         <v>21.49</v>
       </c>
+      <c r="U6" s="50">
+        <v>22.97</v>
+      </c>
     </row>
     <row r="7" spans="1:22" s="3" customFormat="1" ht="15" customHeight="1">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="11">
         <v>30.733214817264763</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="11">
         <v>31.177473779734122</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="12">
         <v>33.000910369941238</v>
       </c>
-      <c r="G7" s="19">
+      <c r="G7" s="13">
         <v>34.727967637310485</v>
       </c>
-      <c r="H7" s="15">
+      <c r="H7" s="14">
         <v>42.433781034604912</v>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="14">
         <v>41.283562941014758</v>
       </c>
-      <c r="J7" s="17">
+      <c r="J7" s="15">
         <v>40.617131725917254</v>
       </c>
-      <c r="K7" s="11">
+      <c r="K7" s="10">
         <v>42.6</v>
       </c>
-      <c r="L7" s="11">
+      <c r="L7" s="10">
         <v>43.3</v>
       </c>
-      <c r="M7" s="11">
+      <c r="M7" s="10">
         <v>38.299999999999997</v>
       </c>
-      <c r="N7" s="11">
+      <c r="N7" s="10">
         <v>33.200000000000003</v>
       </c>
-      <c r="O7" s="11">
+      <c r="O7" s="10">
         <v>34.799999999999997</v>
       </c>
-      <c r="P7" s="11">
+      <c r="P7" s="10">
         <v>35.6</v>
       </c>
-      <c r="Q7" s="11">
+      <c r="Q7" s="10">
         <v>31.9</v>
       </c>
-      <c r="R7" s="59">
+      <c r="R7" s="49">
         <v>26.6</v>
       </c>
       <c r="S7" s="3">
@@ -11122,645 +11103,675 @@
       <c r="T7" s="3">
         <v>32.29</v>
       </c>
+      <c r="U7" s="50">
+        <v>28.43</v>
+      </c>
     </row>
     <row r="8" spans="1:22" customFormat="1" ht="15">
-      <c r="A8" s="68" t="s">
+      <c r="A8" s="57" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="69" t="s">
+      <c r="B8" s="58" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="70" t="s">
+      <c r="C8" s="59" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="71"/>
-      <c r="E8" s="72"/>
-      <c r="F8" s="72"/>
+      <c r="D8" s="60"/>
+      <c r="E8" s="61"/>
+      <c r="F8" s="61"/>
+      <c r="U8" s="62"/>
     </row>
     <row r="9" spans="1:22" s="3" customFormat="1" ht="15" customHeight="1">
-      <c r="A9" s="32" t="s">
+      <c r="A9" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="36" t="s">
+      <c r="C9" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="11">
         <v>25.4</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="11">
         <v>27.2</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="12">
         <v>30.6</v>
       </c>
-      <c r="G9" s="14">
+      <c r="G9" s="13">
         <v>36.1</v>
       </c>
-      <c r="H9" s="15">
+      <c r="H9" s="14">
         <v>40.200000000000003</v>
       </c>
-      <c r="I9" s="16">
+      <c r="I9" s="14">
         <v>44.6</v>
       </c>
-      <c r="J9" s="17">
+      <c r="J9" s="15">
         <v>43.2</v>
       </c>
-      <c r="K9" s="15">
+      <c r="K9" s="14">
         <v>43.3</v>
       </c>
-      <c r="L9" s="15">
+      <c r="L9" s="14">
         <v>38.4</v>
       </c>
-      <c r="M9" s="15">
+      <c r="M9" s="14">
         <v>36.5</v>
       </c>
-      <c r="N9" s="26">
+      <c r="N9" s="23">
         <v>31.2</v>
       </c>
-      <c r="O9" s="26">
+      <c r="O9" s="23">
         <v>30.2</v>
       </c>
-      <c r="P9" s="57">
+      <c r="P9" s="47">
         <v>35.700000000000003</v>
       </c>
-      <c r="Q9" s="57">
+      <c r="Q9" s="47">
         <v>31.2</v>
       </c>
-      <c r="R9" s="57">
+      <c r="R9" s="47">
         <v>24.273948851322064</v>
       </c>
-      <c r="S9" s="60">
+      <c r="S9" s="50">
         <v>26.09501942776404</v>
       </c>
-      <c r="T9" s="60">
+      <c r="T9" s="50">
         <v>28.4</v>
       </c>
-      <c r="V9" s="18"/>
+      <c r="U9" s="50">
+        <v>27.2</v>
+      </c>
+      <c r="V9" s="16"/>
     </row>
     <row r="10" spans="1:22" s="3" customFormat="1" ht="15" customHeight="1">
-      <c r="A10" s="32" t="s">
+      <c r="A10" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="37" t="s">
+      <c r="C10" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="11">
         <v>30.1</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="11">
         <v>33</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="12">
         <v>36.799999999999997</v>
       </c>
-      <c r="G10" s="19">
+      <c r="G10" s="13">
         <v>38.799999999999997</v>
       </c>
-      <c r="H10" s="15">
+      <c r="H10" s="14">
         <v>47.6</v>
       </c>
-      <c r="I10" s="16">
+      <c r="I10" s="14">
         <v>45.3</v>
       </c>
-      <c r="J10" s="17">
+      <c r="J10" s="15">
         <v>44.8</v>
       </c>
-      <c r="K10" s="15">
+      <c r="K10" s="14">
         <v>47.7</v>
       </c>
-      <c r="L10" s="15">
+      <c r="L10" s="14">
         <v>53.5</v>
       </c>
-      <c r="M10" s="15">
+      <c r="M10" s="14">
         <v>39.299999999999997</v>
       </c>
-      <c r="N10" s="26">
+      <c r="N10" s="23">
         <v>34.700000000000003</v>
       </c>
-      <c r="O10" s="26">
+      <c r="O10" s="23">
         <v>36.200000000000003</v>
       </c>
-      <c r="P10" s="57">
+      <c r="P10" s="47">
         <v>38</v>
       </c>
-      <c r="Q10" s="57">
+      <c r="Q10" s="47">
         <v>35.700000000000003</v>
       </c>
-      <c r="R10" s="57">
+      <c r="R10" s="47">
         <v>31.170324930508961</v>
       </c>
-      <c r="S10" s="60">
+      <c r="S10" s="50">
         <v>34.836180341640997</v>
       </c>
-      <c r="T10" s="60">
+      <c r="T10" s="50">
         <v>37.35</v>
       </c>
-      <c r="V10" s="18"/>
+      <c r="U10" s="50">
+        <v>31.68</v>
+      </c>
+      <c r="V10" s="16"/>
     </row>
     <row r="11" spans="1:22" s="3" customFormat="1" ht="15" customHeight="1">
-      <c r="A11" s="32" t="s">
+      <c r="A11" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="37" t="s">
+      <c r="C11" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="21">
+      <c r="D11" s="18">
         <v>27.5</v>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="18">
         <v>27.7</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="12">
         <v>30</v>
       </c>
-      <c r="G11" s="19">
+      <c r="G11" s="13">
         <v>30.2</v>
       </c>
-      <c r="H11" s="15">
+      <c r="H11" s="14">
         <v>31.8</v>
       </c>
-      <c r="I11" s="16">
+      <c r="I11" s="14">
         <v>31.8</v>
       </c>
-      <c r="J11" s="17">
+      <c r="J11" s="15">
         <v>31</v>
       </c>
-      <c r="K11" s="15">
+      <c r="K11" s="14">
         <v>31.8</v>
       </c>
-      <c r="L11" s="15">
+      <c r="L11" s="14">
         <v>45.4</v>
       </c>
-      <c r="M11" s="15">
+      <c r="M11" s="14">
         <v>32.799999999999997</v>
       </c>
-      <c r="N11" s="26">
+      <c r="N11" s="23">
         <v>25.5</v>
       </c>
-      <c r="O11" s="26">
+      <c r="O11" s="23">
         <v>28.8</v>
       </c>
-      <c r="P11" s="57">
+      <c r="P11" s="47">
         <v>25.3</v>
       </c>
-      <c r="Q11" s="57">
+      <c r="Q11" s="47">
         <v>21.3</v>
       </c>
-      <c r="R11" s="57">
+      <c r="R11" s="47">
         <v>23.773041742118217</v>
       </c>
-      <c r="S11" s="60">
+      <c r="S11" s="50">
         <v>15.761291994127298</v>
       </c>
-      <c r="T11" s="60">
+      <c r="T11" s="50">
         <v>18.71</v>
       </c>
-      <c r="V11" s="18"/>
+      <c r="U11" s="50">
+        <v>13.84</v>
+      </c>
+      <c r="V11" s="16"/>
     </row>
     <row r="12" spans="1:22" s="3" customFormat="1" ht="15" customHeight="1">
-      <c r="A12" s="32" t="s">
+      <c r="A12" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="37" t="s">
+      <c r="C12" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="11">
         <v>27.1</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="11">
         <v>23.1</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="12">
         <v>30.4</v>
       </c>
-      <c r="G12" s="19">
+      <c r="G12" s="13">
         <v>29.7</v>
       </c>
-      <c r="H12" s="15">
+      <c r="H12" s="14">
         <v>34.299999999999997</v>
       </c>
-      <c r="I12" s="16">
+      <c r="I12" s="14">
         <v>33</v>
       </c>
-      <c r="J12" s="17">
+      <c r="J12" s="15">
         <v>27.7</v>
       </c>
-      <c r="K12" s="15">
+      <c r="K12" s="14">
         <v>29.2</v>
       </c>
-      <c r="L12" s="15">
+      <c r="L12" s="14">
         <v>30.3</v>
       </c>
-      <c r="M12" s="15">
+      <c r="M12" s="14">
         <v>29.1</v>
       </c>
-      <c r="N12" s="26">
+      <c r="N12" s="23">
         <v>20.2</v>
       </c>
-      <c r="O12" s="26">
+      <c r="O12" s="23">
         <v>22.7</v>
       </c>
-      <c r="P12" s="57">
+      <c r="P12" s="47">
         <v>20.8</v>
       </c>
-      <c r="Q12" s="57">
+      <c r="Q12" s="47">
         <v>20.100000000000001</v>
       </c>
-      <c r="R12" s="57">
+      <c r="R12" s="47">
         <v>17.885950761029672</v>
       </c>
-      <c r="S12" s="60">
+      <c r="S12" s="50">
         <v>12.708498808578236</v>
       </c>
-      <c r="T12" s="60">
+      <c r="T12" s="50">
         <v>19.7</v>
       </c>
-      <c r="V12" s="18"/>
+      <c r="U12" s="50">
+        <v>17.940000000000001</v>
+      </c>
+      <c r="V12" s="16"/>
     </row>
     <row r="13" spans="1:22" s="3" customFormat="1" ht="15" customHeight="1">
-      <c r="A13" s="32" t="s">
+      <c r="A13" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="37" t="s">
+      <c r="C13" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="11">
         <v>27.1</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="11">
         <v>27.1</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="12">
         <v>30.4</v>
       </c>
-      <c r="G13" s="22">
+      <c r="G13" s="19">
         <v>33</v>
       </c>
-      <c r="H13" s="15">
+      <c r="H13" s="14">
         <v>43.2</v>
       </c>
-      <c r="I13" s="16">
+      <c r="I13" s="14">
         <v>44</v>
       </c>
-      <c r="J13" s="17">
+      <c r="J13" s="15">
         <v>43.4</v>
       </c>
-      <c r="K13" s="15">
+      <c r="K13" s="14">
         <v>45.8</v>
       </c>
-      <c r="L13" s="15">
+      <c r="L13" s="14">
         <v>72.3</v>
       </c>
-      <c r="M13" s="15">
+      <c r="M13" s="14">
         <v>41.6</v>
       </c>
-      <c r="N13" s="26">
+      <c r="N13" s="23">
         <v>38.5</v>
       </c>
-      <c r="O13" s="26">
+      <c r="O13" s="23">
         <v>35.200000000000003</v>
       </c>
-      <c r="P13" s="57">
+      <c r="P13" s="47">
         <v>37.9</v>
       </c>
-      <c r="Q13" s="57">
+      <c r="Q13" s="47">
         <v>35.6</v>
       </c>
-      <c r="R13" s="57">
+      <c r="R13" s="47">
         <v>27.236016839934702</v>
       </c>
-      <c r="S13" s="60">
+      <c r="S13" s="50">
         <v>36.667303251792568</v>
       </c>
-      <c r="T13" s="60">
+      <c r="T13" s="50">
         <v>40.06</v>
       </c>
-      <c r="V13" s="18"/>
+      <c r="U13" s="50">
+        <v>36.65</v>
+      </c>
+      <c r="V13" s="16"/>
     </row>
     <row r="14" spans="1:22" s="3" customFormat="1" ht="15" customHeight="1">
-      <c r="A14" s="32" t="s">
+      <c r="A14" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="37" t="s">
+      <c r="C14" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="11">
         <v>39.9</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="11">
         <v>38.9</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="12">
         <v>46.4</v>
       </c>
-      <c r="G14" s="19">
+      <c r="G14" s="13">
         <v>48.5</v>
       </c>
-      <c r="H14" s="15">
+      <c r="H14" s="14">
         <v>59.3</v>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="14">
         <v>58.8</v>
       </c>
-      <c r="J14" s="17">
+      <c r="J14" s="15">
         <v>61</v>
       </c>
-      <c r="K14" s="15">
+      <c r="K14" s="14">
         <v>58.2</v>
       </c>
-      <c r="L14" s="15">
+      <c r="L14" s="14">
         <v>36.4</v>
       </c>
-      <c r="M14" s="15">
+      <c r="M14" s="14">
         <v>41.9</v>
       </c>
-      <c r="N14" s="26">
+      <c r="N14" s="23">
         <v>34.9</v>
       </c>
-      <c r="O14" s="26">
+      <c r="O14" s="23">
         <v>37.1</v>
       </c>
-      <c r="P14" s="57">
+      <c r="P14" s="47">
         <v>34.1</v>
       </c>
-      <c r="Q14" s="57">
+      <c r="Q14" s="47">
         <v>27.2</v>
       </c>
-      <c r="R14" s="57">
+      <c r="R14" s="47">
         <v>24.736924768336735</v>
       </c>
-      <c r="S14" s="60">
+      <c r="S14" s="50">
         <v>21.147798742138363</v>
       </c>
-      <c r="T14" s="60">
+      <c r="T14" s="50">
         <v>23.27</v>
       </c>
-      <c r="V14" s="18"/>
+      <c r="U14" s="50">
+        <v>17.48</v>
+      </c>
+      <c r="V14" s="16"/>
     </row>
     <row r="15" spans="1:22" s="3" customFormat="1" ht="15" customHeight="1">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="37" t="s">
+      <c r="C15" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="11">
         <v>38.4</v>
       </c>
-      <c r="E15" s="12">
+      <c r="E15" s="11">
         <v>40.1</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="12">
         <v>39.299999999999997</v>
       </c>
-      <c r="G15" s="19">
+      <c r="G15" s="13">
         <v>44</v>
       </c>
-      <c r="H15" s="15">
+      <c r="H15" s="14">
         <v>49.1</v>
       </c>
-      <c r="I15" s="16">
+      <c r="I15" s="14">
         <v>50.3</v>
       </c>
-      <c r="J15" s="17">
+      <c r="J15" s="15">
         <v>52</v>
       </c>
-      <c r="K15" s="15">
+      <c r="K15" s="14">
         <v>50.8</v>
       </c>
-      <c r="L15" s="15">
+      <c r="L15" s="14">
         <v>59.7</v>
       </c>
-      <c r="M15" s="15">
+      <c r="M15" s="14">
         <v>47.8</v>
       </c>
-      <c r="N15" s="26">
+      <c r="N15" s="23">
         <v>46.4</v>
       </c>
-      <c r="O15" s="26">
+      <c r="O15" s="23">
         <v>52.1</v>
       </c>
-      <c r="P15" s="57">
+      <c r="P15" s="47">
         <v>51</v>
       </c>
-      <c r="Q15" s="57">
+      <c r="Q15" s="47">
         <v>44.5</v>
       </c>
-      <c r="R15" s="57">
+      <c r="R15" s="47">
         <v>38.926974664679584</v>
       </c>
-      <c r="S15" s="60">
+      <c r="S15" s="50">
         <v>33.139030137665877</v>
       </c>
-      <c r="T15" s="60">
+      <c r="T15" s="50">
         <v>30.23</v>
       </c>
-      <c r="V15" s="18"/>
+      <c r="U15" s="50">
+        <v>27.7</v>
+      </c>
+      <c r="V15" s="16"/>
     </row>
     <row r="16" spans="1:22" s="3" customFormat="1" ht="15" customHeight="1">
-      <c r="A16" s="33" t="s">
+      <c r="A16" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="37" t="s">
+      <c r="C16" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="11">
         <v>25.9</v>
       </c>
-      <c r="E16" s="12">
+      <c r="E16" s="11">
         <v>24.8</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="12">
         <v>17.899999999999999</v>
       </c>
-      <c r="G16" s="23">
+      <c r="G16" s="20">
         <v>20.399999999999999</v>
       </c>
-      <c r="H16" s="15">
+      <c r="H16" s="14">
         <v>25.3</v>
       </c>
-      <c r="I16" s="16">
+      <c r="I16" s="14">
         <v>26</v>
       </c>
-      <c r="J16" s="17">
+      <c r="J16" s="15">
         <v>26.6</v>
       </c>
-      <c r="K16" s="15">
+      <c r="K16" s="14">
         <v>26.5</v>
       </c>
-      <c r="L16" s="15">
+      <c r="L16" s="14">
         <v>22.1</v>
       </c>
-      <c r="M16" s="15">
+      <c r="M16" s="14">
         <v>21.4</v>
       </c>
-      <c r="N16" s="26">
+      <c r="N16" s="23">
         <v>17.399999999999999</v>
       </c>
-      <c r="O16" s="26">
+      <c r="O16" s="23">
         <v>24.3</v>
       </c>
-      <c r="P16" s="57">
+      <c r="P16" s="47">
         <v>28.9</v>
       </c>
-      <c r="Q16" s="57">
+      <c r="Q16" s="47">
         <v>22.2</v>
       </c>
-      <c r="R16" s="57">
+      <c r="R16" s="47">
         <v>23.305151831797598</v>
       </c>
-      <c r="S16" s="61">
+      <c r="S16" s="50">
         <v>22.34784446322908</v>
       </c>
-      <c r="T16" s="61">
+      <c r="T16" s="50">
         <v>6.48</v>
       </c>
-      <c r="V16" s="18"/>
+      <c r="U16" s="50">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="V16" s="16"/>
     </row>
     <row r="17" spans="1:22" s="3" customFormat="1" ht="15" customHeight="1" thickBot="1">
-      <c r="A17" s="34" t="s">
+      <c r="A17" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="39" t="s">
+      <c r="B17" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="38" t="s">
+      <c r="C17" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="D17" s="40">
+      <c r="D17" s="35">
         <v>24.2</v>
       </c>
-      <c r="E17" s="40">
+      <c r="E17" s="35">
         <v>26</v>
       </c>
-      <c r="F17" s="41">
+      <c r="F17" s="36">
         <v>23.9</v>
       </c>
-      <c r="G17" s="42">
+      <c r="G17" s="37">
         <v>27</v>
       </c>
-      <c r="H17" s="43">
+      <c r="H17" s="38">
         <v>36.1</v>
       </c>
-      <c r="I17" s="44">
+      <c r="I17" s="38">
         <v>43.9</v>
       </c>
-      <c r="J17" s="45">
+      <c r="J17" s="39">
         <v>46.7</v>
       </c>
-      <c r="K17" s="43">
+      <c r="K17" s="38">
         <v>54.9</v>
       </c>
-      <c r="L17" s="43">
+      <c r="L17" s="38">
         <v>52.8</v>
       </c>
-      <c r="M17" s="43">
+      <c r="M17" s="38">
         <v>52.6</v>
       </c>
-      <c r="N17" s="46">
+      <c r="N17" s="40">
         <v>51.6</v>
       </c>
-      <c r="O17" s="55">
+      <c r="O17" s="45">
         <v>65</v>
       </c>
-      <c r="P17" s="55">
+      <c r="P17" s="45">
         <v>77</v>
       </c>
-      <c r="Q17" s="55">
+      <c r="Q17" s="45">
         <v>63.7</v>
       </c>
-      <c r="R17" s="55">
+      <c r="R17" s="45">
         <v>69.352892024881626</v>
       </c>
-      <c r="S17" s="62">
+      <c r="S17" s="51">
         <v>51.037459963793346</v>
       </c>
-      <c r="T17" s="62">
+      <c r="T17" s="51">
         <v>30.85</v>
       </c>
-      <c r="V17" s="18"/>
+      <c r="U17" s="51">
+        <v>39.97</v>
+      </c>
+      <c r="V17" s="16"/>
     </row>
     <row r="18" spans="1:22" s="3" customFormat="1" ht="12">
-      <c r="B18" s="47"/>
-      <c r="C18" s="47"/>
-      <c r="D18" s="47"/>
-      <c r="E18" s="47"/>
-      <c r="F18" s="47"/>
-      <c r="G18" s="48"/>
-      <c r="H18" s="48"/>
-      <c r="I18" s="49"/>
-      <c r="J18" s="48"/>
-      <c r="K18" s="48"/>
-      <c r="L18" s="48"/>
-      <c r="M18" s="48"/>
-      <c r="N18" s="48"/>
-      <c r="O18" s="50"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="41"/>
+      <c r="I18" s="41"/>
+      <c r="J18" s="41"/>
+      <c r="K18" s="41"/>
+      <c r="L18" s="41"/>
+      <c r="M18" s="41"/>
+      <c r="N18" s="41"/>
     </row>
     <row r="19" spans="1:22">
-      <c r="B19" s="24"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
+      <c r="B19" s="21"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
     </row>
     <row r="20" spans="1:22">
-      <c r="B20" s="24"/>
-      <c r="C20" s="24"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="24"/>
+      <c r="B20" s="21"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
     </row>
     <row r="21" spans="1:22">
-      <c r="B21" s="24"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
     </row>
     <row r="22" spans="1:22">
-      <c r="B22" s="24"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
     </row>
     <row r="23" spans="1:22">
-      <c r="B23" s="24"/>
-      <c r="C23" s="24"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
     </row>
     <row r="24" spans="1:22">
-      <c r="B24" s="24"/>
-      <c r="C24" s="24"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="24"/>
-      <c r="F24" s="24"/>
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.51181102362204722" right="0.31496062992125984" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
